--- a/data/purchase2526.xlsx
+++ b/data/purchase2526.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24026"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89716A5A-219C-4DCB-97A2-69976D1EA5C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A93B7061-BA14-4E88-81F2-5FB9A8F726C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6352" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6622" uniqueCount="421">
   <si>
     <t>State Office</t>
   </si>
@@ -1266,6 +1266,21 @@
   </si>
   <si>
     <t>7002553830</t>
+  </si>
+  <si>
+    <t>IOC CLEARBLUE IOC CLEARBLUE IOC CLEARBLUE</t>
+  </si>
+  <si>
+    <t>1-1479771745984</t>
+  </si>
+  <si>
+    <t>7003491171</t>
+  </si>
+  <si>
+    <t>SERVO GREASE MP 3 SERVO GREASE MP 3 SERVO GREASE MP 3 SERVO GREASE MP 3</t>
+  </si>
+  <si>
+    <t>SERVO SUPER 20W-40 MG SERVO SUPER 20W-40 MG SERVO SUPER 20W-40 MG SERVO SUPER 20W-40 MG</t>
   </si>
 </sst>
 </file>
@@ -1275,7 +1290,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1286,6 +1301,11 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1363,7 +1383,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1406,6 +1426,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1745,7 +1780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AK352"/>
+  <dimension ref="A1:AK367"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.109375" customWidth="1"/>
@@ -40203,6 +40238,1669 @@
         <v>0.09</v>
       </c>
     </row>
+    <row r="353" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A353" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B353" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C353" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D353" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E353" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F353" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="G353" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="H353" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="I353" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="J353" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="K353" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="L353" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="M353" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="N353" s="16">
+        <v>20</v>
+      </c>
+      <c r="O353" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="P353" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q353" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="R353" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="S353" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="T353" s="17">
+        <v>46076</v>
+      </c>
+      <c r="U353" s="18">
+        <v>5</v>
+      </c>
+      <c r="V353" s="18">
+        <v>100</v>
+      </c>
+      <c r="W353" s="18">
+        <v>6500</v>
+      </c>
+      <c r="X353" s="18">
+        <v>4225</v>
+      </c>
+      <c r="Y353" s="18">
+        <v>4819.93</v>
+      </c>
+      <c r="Z353" s="7"/>
+      <c r="AA353" s="7"/>
+      <c r="AB353" s="18">
+        <v>-170.63</v>
+      </c>
+      <c r="AC353" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD353" s="7"/>
+      <c r="AE353" s="18">
+        <v>-92.99</v>
+      </c>
+      <c r="AF353" s="18">
+        <v>4556.3100000000004</v>
+      </c>
+      <c r="AG353" s="18">
+        <v>5376.45</v>
+      </c>
+      <c r="AH353" s="18">
+        <v>0</v>
+      </c>
+      <c r="AI353" s="18">
+        <v>820.14</v>
+      </c>
+      <c r="AJ353" s="18">
+        <v>5376.45</v>
+      </c>
+      <c r="AK353" s="19">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="354" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A354" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B354" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C354" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D354" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E354" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F354" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="G354" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="H354" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="I354" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J354" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="K354" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="L354" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="M354" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="N354" s="16">
+        <v>20</v>
+      </c>
+      <c r="O354" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="P354" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q354" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="R354" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="S354" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="T354" s="17">
+        <v>46076</v>
+      </c>
+      <c r="U354" s="18">
+        <v>10</v>
+      </c>
+      <c r="V354" s="18">
+        <v>200</v>
+      </c>
+      <c r="W354" s="18">
+        <v>67800</v>
+      </c>
+      <c r="X354" s="18">
+        <v>44070</v>
+      </c>
+      <c r="Y354" s="18">
+        <v>44272.95</v>
+      </c>
+      <c r="Z354" s="7"/>
+      <c r="AA354" s="18">
+        <v>-1200</v>
+      </c>
+      <c r="AB354" s="18">
+        <v>-2873.31</v>
+      </c>
+      <c r="AC354" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD354" s="18">
+        <v>-100</v>
+      </c>
+      <c r="AE354" s="18">
+        <v>-801.99</v>
+      </c>
+      <c r="AF354" s="18">
+        <v>39297.65</v>
+      </c>
+      <c r="AG354" s="18">
+        <v>46371.23</v>
+      </c>
+      <c r="AH354" s="18">
+        <v>0</v>
+      </c>
+      <c r="AI354" s="18">
+        <v>7073.58</v>
+      </c>
+      <c r="AJ354" s="18">
+        <v>46371.23</v>
+      </c>
+      <c r="AK354" s="19">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="355" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A355" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B355" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C355" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D355" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E355" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F355" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="G355" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="H355" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="I355" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="J355" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="K355" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="L355" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="M355" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="N355" s="16">
+        <v>14</v>
+      </c>
+      <c r="O355" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="P355" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q355" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="R355" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="S355" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="T355" s="17">
+        <v>46076</v>
+      </c>
+      <c r="U355" s="18">
+        <v>7</v>
+      </c>
+      <c r="V355" s="18">
+        <v>98</v>
+      </c>
+      <c r="W355" s="18">
+        <v>35196</v>
+      </c>
+      <c r="X355" s="18">
+        <v>22877.4</v>
+      </c>
+      <c r="Y355" s="18">
+        <v>23749.61</v>
+      </c>
+      <c r="Z355" s="7"/>
+      <c r="AA355" s="18">
+        <v>-2058</v>
+      </c>
+      <c r="AB355" s="18">
+        <v>-1541.35</v>
+      </c>
+      <c r="AC355" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD355" s="18">
+        <v>-49</v>
+      </c>
+      <c r="AE355" s="18">
+        <v>-402.03</v>
+      </c>
+      <c r="AF355" s="18">
+        <v>19699.23</v>
+      </c>
+      <c r="AG355" s="18">
+        <v>23245.09</v>
+      </c>
+      <c r="AH355" s="18">
+        <v>0</v>
+      </c>
+      <c r="AI355" s="18">
+        <v>3545.86</v>
+      </c>
+      <c r="AJ355" s="18">
+        <v>23245.09</v>
+      </c>
+      <c r="AK355" s="19">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="356" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A356" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B356" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C356" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D356" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E356" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F356" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="G356" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="H356" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="I356" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="J356" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="K356" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="L356" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="M356" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="N356" s="16">
+        <v>20</v>
+      </c>
+      <c r="O356" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="P356" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q356" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="R356" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="S356" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="T356" s="17">
+        <v>46076</v>
+      </c>
+      <c r="U356" s="18">
+        <v>2</v>
+      </c>
+      <c r="V356" s="18">
+        <v>40</v>
+      </c>
+      <c r="W356" s="18">
+        <v>13000</v>
+      </c>
+      <c r="X356" s="18">
+        <v>8294</v>
+      </c>
+      <c r="Y356" s="18">
+        <v>8094.95</v>
+      </c>
+      <c r="Z356" s="18">
+        <v>-200</v>
+      </c>
+      <c r="AA356" s="18">
+        <v>-400</v>
+      </c>
+      <c r="AB356" s="18">
+        <v>-525.36</v>
+      </c>
+      <c r="AC356" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD356" s="18">
+        <v>-20</v>
+      </c>
+      <c r="AE356" s="18">
+        <v>-138.99</v>
+      </c>
+      <c r="AF356" s="18">
+        <v>6810.6</v>
+      </c>
+      <c r="AG356" s="18">
+        <v>8036.51</v>
+      </c>
+      <c r="AH356" s="18">
+        <v>0</v>
+      </c>
+      <c r="AI356" s="18">
+        <v>1225.9100000000001</v>
+      </c>
+      <c r="AJ356" s="18">
+        <v>8036.51</v>
+      </c>
+      <c r="AK356" s="19">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="357" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A357" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B357" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C357" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D357" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E357" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F357" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="G357" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="H357" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="I357" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="J357" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="K357" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="L357" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="M357" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="N357" s="16">
+        <v>5</v>
+      </c>
+      <c r="O357" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="P357" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q357" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="R357" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="S357" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="T357" s="17">
+        <v>46076</v>
+      </c>
+      <c r="U357" s="18">
+        <v>2</v>
+      </c>
+      <c r="V357" s="18">
+        <v>10</v>
+      </c>
+      <c r="W357" s="18">
+        <v>4060</v>
+      </c>
+      <c r="X357" s="18">
+        <v>2639</v>
+      </c>
+      <c r="Y357" s="18">
+        <v>2814.13</v>
+      </c>
+      <c r="Z357" s="7"/>
+      <c r="AA357" s="18">
+        <v>-450</v>
+      </c>
+      <c r="AB357" s="18">
+        <v>-215.84</v>
+      </c>
+      <c r="AC357" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD357" s="18">
+        <v>-5</v>
+      </c>
+      <c r="AE357" s="18">
+        <v>-42.87</v>
+      </c>
+      <c r="AF357" s="18">
+        <v>2100.42</v>
+      </c>
+      <c r="AG357" s="18">
+        <v>2478.5</v>
+      </c>
+      <c r="AH357" s="18">
+        <v>0</v>
+      </c>
+      <c r="AI357" s="18">
+        <v>378.08</v>
+      </c>
+      <c r="AJ357" s="18">
+        <v>2478.5</v>
+      </c>
+      <c r="AK357" s="19">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="358" spans="1:37" ht="40.799999999999997" x14ac:dyDescent="0.3">
+      <c r="A358" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B358" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C358" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D358" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E358" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F358" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="G358" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="H358" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="I358" s="15" t="s">
+        <v>419</v>
+      </c>
+      <c r="J358" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="K358" s="15" t="s">
+        <v>332</v>
+      </c>
+      <c r="L358" s="15" t="s">
+        <v>333</v>
+      </c>
+      <c r="M358" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="N358" s="16">
+        <v>12</v>
+      </c>
+      <c r="O358" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="P358" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q358" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="R358" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="S358" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="T358" s="17">
+        <v>46076</v>
+      </c>
+      <c r="U358" s="18">
+        <v>1</v>
+      </c>
+      <c r="V358" s="18">
+        <v>12</v>
+      </c>
+      <c r="W358" s="18">
+        <v>4084</v>
+      </c>
+      <c r="X358" s="18">
+        <v>3211</v>
+      </c>
+      <c r="Y358" s="18">
+        <v>3035.97</v>
+      </c>
+      <c r="Z358" s="7"/>
+      <c r="AA358" s="18">
+        <v>-540</v>
+      </c>
+      <c r="AB358" s="18">
+        <v>-232.86</v>
+      </c>
+      <c r="AC358" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD358" s="18">
+        <v>-6</v>
+      </c>
+      <c r="AE358" s="18">
+        <v>-45.14</v>
+      </c>
+      <c r="AF358" s="18">
+        <v>2211.9699999999998</v>
+      </c>
+      <c r="AG358" s="18">
+        <v>2610.12</v>
+      </c>
+      <c r="AH358" s="18">
+        <v>0</v>
+      </c>
+      <c r="AI358" s="18">
+        <v>398.15</v>
+      </c>
+      <c r="AJ358" s="18">
+        <v>2610.12</v>
+      </c>
+      <c r="AK358" s="19">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="359" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A359" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B359" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C359" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D359" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E359" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F359" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="G359" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="H359" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="I359" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="J359" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="K359" s="15" t="s">
+        <v>292</v>
+      </c>
+      <c r="L359" s="15" t="s">
+        <v>293</v>
+      </c>
+      <c r="M359" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="N359" s="16">
+        <v>20</v>
+      </c>
+      <c r="O359" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="P359" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q359" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="R359" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="S359" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="T359" s="17">
+        <v>46076</v>
+      </c>
+      <c r="U359" s="18">
+        <v>10</v>
+      </c>
+      <c r="V359" s="18">
+        <v>200</v>
+      </c>
+      <c r="W359" s="18">
+        <v>67800</v>
+      </c>
+      <c r="X359" s="18">
+        <v>44070</v>
+      </c>
+      <c r="Y359" s="18">
+        <v>45164.12</v>
+      </c>
+      <c r="Z359" s="18">
+        <v>-1000</v>
+      </c>
+      <c r="AA359" s="18">
+        <v>-6600</v>
+      </c>
+      <c r="AB359" s="18">
+        <v>-3464.08</v>
+      </c>
+      <c r="AC359" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD359" s="18">
+        <v>-100</v>
+      </c>
+      <c r="AE359" s="18">
+        <v>-680</v>
+      </c>
+      <c r="AF359" s="18">
+        <v>33320.04</v>
+      </c>
+      <c r="AG359" s="18">
+        <v>39317.65</v>
+      </c>
+      <c r="AH359" s="18">
+        <v>0</v>
+      </c>
+      <c r="AI359" s="18">
+        <v>5997.61</v>
+      </c>
+      <c r="AJ359" s="18">
+        <v>39317.65</v>
+      </c>
+      <c r="AK359" s="19">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="360" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A360" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B360" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C360" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D360" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E360" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F360" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="G360" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="H360" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="I360" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="J360" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="K360" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="L360" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="M360" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="N360" s="16">
+        <v>15</v>
+      </c>
+      <c r="O360" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="P360" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q360" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="R360" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="S360" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="T360" s="17">
+        <v>46076</v>
+      </c>
+      <c r="U360" s="18">
+        <v>9</v>
+      </c>
+      <c r="V360" s="18">
+        <v>135</v>
+      </c>
+      <c r="W360" s="18">
+        <v>45225</v>
+      </c>
+      <c r="X360" s="18">
+        <v>29396.25</v>
+      </c>
+      <c r="Y360" s="18">
+        <v>30256.76</v>
+      </c>
+      <c r="Z360" s="18">
+        <v>-675</v>
+      </c>
+      <c r="AA360" s="18">
+        <v>-3510</v>
+      </c>
+      <c r="AB360" s="18">
+        <v>-2320.69</v>
+      </c>
+      <c r="AC360" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD360" s="18">
+        <v>-67.5</v>
+      </c>
+      <c r="AE360" s="18">
+        <v>-473.67</v>
+      </c>
+      <c r="AF360" s="18">
+        <v>23209.9</v>
+      </c>
+      <c r="AG360" s="18">
+        <v>27387.68</v>
+      </c>
+      <c r="AH360" s="18">
+        <v>0</v>
+      </c>
+      <c r="AI360" s="18">
+        <v>4177.78</v>
+      </c>
+      <c r="AJ360" s="18">
+        <v>27387.68</v>
+      </c>
+      <c r="AK360" s="19">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="361" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A361" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B361" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C361" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D361" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E361" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F361" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="G361" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="H361" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="I361" s="15" t="s">
+        <v>410</v>
+      </c>
+      <c r="J361" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="K361" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="L361" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="M361" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="N361" s="16">
+        <v>210</v>
+      </c>
+      <c r="O361" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="P361" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q361" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="R361" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="S361" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="T361" s="17">
+        <v>46076</v>
+      </c>
+      <c r="U361" s="18">
+        <v>2</v>
+      </c>
+      <c r="V361" s="18">
+        <v>420</v>
+      </c>
+      <c r="W361" s="7"/>
+      <c r="X361" s="18">
+        <v>91140</v>
+      </c>
+      <c r="Y361" s="7"/>
+      <c r="Z361" s="7"/>
+      <c r="AA361" s="18">
+        <v>-6720</v>
+      </c>
+      <c r="AB361" s="18">
+        <v>0</v>
+      </c>
+      <c r="AC361" s="18">
+        <v>-5924.1</v>
+      </c>
+      <c r="AD361" s="18">
+        <v>-210</v>
+      </c>
+      <c r="AE361" s="18">
+        <v>-1565.72</v>
+      </c>
+      <c r="AF361" s="18">
+        <v>76720.179999999993</v>
+      </c>
+      <c r="AG361" s="18">
+        <v>90529.81</v>
+      </c>
+      <c r="AH361" s="18">
+        <v>0</v>
+      </c>
+      <c r="AI361" s="18">
+        <v>13809.63</v>
+      </c>
+      <c r="AJ361" s="18">
+        <v>90529.81</v>
+      </c>
+      <c r="AK361" s="19">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="362" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A362" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B362" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C362" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D362" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E362" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F362" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="G362" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="H362" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="I362" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="J362" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="K362" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="L362" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="M362" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="N362" s="16">
+        <v>15</v>
+      </c>
+      <c r="O362" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="P362" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q362" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="R362" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="S362" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="T362" s="17">
+        <v>46076</v>
+      </c>
+      <c r="U362" s="18">
+        <v>7</v>
+      </c>
+      <c r="V362" s="18">
+        <v>105</v>
+      </c>
+      <c r="W362" s="18">
+        <v>35175</v>
+      </c>
+      <c r="X362" s="18">
+        <v>22863.75</v>
+      </c>
+      <c r="Y362" s="18">
+        <v>23701.16</v>
+      </c>
+      <c r="Z362" s="7"/>
+      <c r="AA362" s="18">
+        <v>-5565</v>
+      </c>
+      <c r="AB362" s="18">
+        <v>-1817.87</v>
+      </c>
+      <c r="AC362" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD362" s="18">
+        <v>-52.5</v>
+      </c>
+      <c r="AE362" s="18">
+        <v>-325.32</v>
+      </c>
+      <c r="AF362" s="18">
+        <v>15940.47</v>
+      </c>
+      <c r="AG362" s="18">
+        <v>18809.75</v>
+      </c>
+      <c r="AH362" s="18">
+        <v>0</v>
+      </c>
+      <c r="AI362" s="18">
+        <v>2869.28</v>
+      </c>
+      <c r="AJ362" s="18">
+        <v>18809.75</v>
+      </c>
+      <c r="AK362" s="19">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="363" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A363" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B363" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C363" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D363" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E363" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F363" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="G363" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="H363" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="I363" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="J363" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="K363" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="L363" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="M363" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="N363" s="16">
+        <v>20</v>
+      </c>
+      <c r="O363" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="P363" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q363" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="R363" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="S363" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="T363" s="17">
+        <v>46076</v>
+      </c>
+      <c r="U363" s="18">
+        <v>2</v>
+      </c>
+      <c r="V363" s="18">
+        <v>40</v>
+      </c>
+      <c r="W363" s="18">
+        <v>15800</v>
+      </c>
+      <c r="X363" s="18">
+        <v>10270</v>
+      </c>
+      <c r="Y363" s="18">
+        <v>10456.68</v>
+      </c>
+      <c r="Z363" s="7"/>
+      <c r="AA363" s="18">
+        <v>-1640</v>
+      </c>
+      <c r="AB363" s="18">
+        <v>-802.03</v>
+      </c>
+      <c r="AC363" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD363" s="18">
+        <v>-20</v>
+      </c>
+      <c r="AE363" s="18">
+        <v>-159.88999999999999</v>
+      </c>
+      <c r="AF363" s="18">
+        <v>7834.76</v>
+      </c>
+      <c r="AG363" s="18">
+        <v>9245.02</v>
+      </c>
+      <c r="AH363" s="18">
+        <v>0</v>
+      </c>
+      <c r="AI363" s="18">
+        <v>1410.26</v>
+      </c>
+      <c r="AJ363" s="18">
+        <v>9245.02</v>
+      </c>
+      <c r="AK363" s="19">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="364" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A364" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B364" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C364" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D364" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E364" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F364" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="G364" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="H364" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="I364" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="J364" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="K364" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="L364" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="M364" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="N364" s="16">
+        <v>20</v>
+      </c>
+      <c r="O364" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="P364" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q364" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="R364" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="S364" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="T364" s="17">
+        <v>46076</v>
+      </c>
+      <c r="U364" s="18">
+        <v>10</v>
+      </c>
+      <c r="V364" s="18">
+        <v>200</v>
+      </c>
+      <c r="W364" s="18">
+        <v>62400</v>
+      </c>
+      <c r="X364" s="18">
+        <v>40560</v>
+      </c>
+      <c r="Y364" s="18">
+        <v>40264.5</v>
+      </c>
+      <c r="Z364" s="7"/>
+      <c r="AA364" s="18">
+        <v>0</v>
+      </c>
+      <c r="AB364" s="18">
+        <v>-3088.28</v>
+      </c>
+      <c r="AC364" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD364" s="18">
+        <v>-100</v>
+      </c>
+      <c r="AE364" s="18">
+        <v>-741.52</v>
+      </c>
+      <c r="AF364" s="18">
+        <v>36334.699999999997</v>
+      </c>
+      <c r="AG364" s="18">
+        <v>42874.95</v>
+      </c>
+      <c r="AH364" s="18">
+        <v>0</v>
+      </c>
+      <c r="AI364" s="18">
+        <v>6540.25</v>
+      </c>
+      <c r="AJ364" s="18">
+        <v>42874.95</v>
+      </c>
+      <c r="AK364" s="19">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="365" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A365" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B365" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C365" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D365" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E365" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F365" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="G365" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="H365" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="I365" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="J365" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="K365" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="L365" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="M365" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="N365" s="16">
+        <v>20</v>
+      </c>
+      <c r="O365" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="P365" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q365" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="R365" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="S365" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="T365" s="17">
+        <v>46076</v>
+      </c>
+      <c r="U365" s="18">
+        <v>10</v>
+      </c>
+      <c r="V365" s="18">
+        <v>200</v>
+      </c>
+      <c r="W365" s="18">
+        <v>60400</v>
+      </c>
+      <c r="X365" s="18">
+        <v>39260</v>
+      </c>
+      <c r="Y365" s="18">
+        <v>39252.43</v>
+      </c>
+      <c r="Z365" s="7"/>
+      <c r="AA365" s="18">
+        <v>-2600</v>
+      </c>
+      <c r="AB365" s="18">
+        <v>-3010.65</v>
+      </c>
+      <c r="AC365" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD365" s="18">
+        <v>-100</v>
+      </c>
+      <c r="AE365" s="18">
+        <v>-670.84</v>
+      </c>
+      <c r="AF365" s="18">
+        <v>32870.94</v>
+      </c>
+      <c r="AG365" s="18">
+        <v>38787.71</v>
+      </c>
+      <c r="AH365" s="18">
+        <v>0</v>
+      </c>
+      <c r="AI365" s="18">
+        <v>5916.77</v>
+      </c>
+      <c r="AJ365" s="18">
+        <v>38787.71</v>
+      </c>
+      <c r="AK365" s="19">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="366" spans="1:37" ht="40.799999999999997" x14ac:dyDescent="0.3">
+      <c r="A366" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B366" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C366" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D366" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E366" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F366" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="G366" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="H366" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="I366" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="J366" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="K366" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="L366" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="M366" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="N366" s="16">
+        <v>20</v>
+      </c>
+      <c r="O366" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="P366" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q366" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="R366" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="S366" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="T366" s="17">
+        <v>46076</v>
+      </c>
+      <c r="U366" s="18">
+        <v>6</v>
+      </c>
+      <c r="V366" s="18">
+        <v>120</v>
+      </c>
+      <c r="W366" s="18">
+        <v>34440</v>
+      </c>
+      <c r="X366" s="18">
+        <v>22386</v>
+      </c>
+      <c r="Y366" s="18">
+        <v>22341.7</v>
+      </c>
+      <c r="Z366" s="7"/>
+      <c r="AA366" s="18">
+        <v>-2880</v>
+      </c>
+      <c r="AB366" s="18">
+        <v>-1713.6</v>
+      </c>
+      <c r="AC366" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD366" s="18">
+        <v>-60</v>
+      </c>
+      <c r="AE366" s="18">
+        <v>-353.76</v>
+      </c>
+      <c r="AF366" s="18">
+        <v>17334.34</v>
+      </c>
+      <c r="AG366" s="18">
+        <v>20454.52</v>
+      </c>
+      <c r="AH366" s="18">
+        <v>0</v>
+      </c>
+      <c r="AI366" s="18">
+        <v>3120.18</v>
+      </c>
+      <c r="AJ366" s="18">
+        <v>20454.52</v>
+      </c>
+      <c r="AK366" s="19">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="367" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A367" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B367" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C367" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D367" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E367" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F367" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="G367" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="H367" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="I367" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="J367" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="K367" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="L367" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="M367" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="N367" s="16">
+        <v>20</v>
+      </c>
+      <c r="O367" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="P367" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q367" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="R367" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="S367" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="T367" s="17">
+        <v>46076</v>
+      </c>
+      <c r="U367" s="18">
+        <v>10</v>
+      </c>
+      <c r="V367" s="18">
+        <v>200</v>
+      </c>
+      <c r="W367" s="18">
+        <v>75000</v>
+      </c>
+      <c r="X367" s="18">
+        <v>48750</v>
+      </c>
+      <c r="Y367" s="18">
+        <v>48373.23</v>
+      </c>
+      <c r="Z367" s="7"/>
+      <c r="AA367" s="18">
+        <v>-3200</v>
+      </c>
+      <c r="AB367" s="18">
+        <v>-3710.22</v>
+      </c>
+      <c r="AC367" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD367" s="18">
+        <v>-100</v>
+      </c>
+      <c r="AE367" s="18">
+        <v>-827.26</v>
+      </c>
+      <c r="AF367" s="18">
+        <v>40535.75</v>
+      </c>
+      <c r="AG367" s="18">
+        <v>47832.19</v>
+      </c>
+      <c r="AH367" s="18">
+        <v>0</v>
+      </c>
+      <c r="AI367" s="18">
+        <v>7296.44</v>
+      </c>
+      <c r="AJ367" s="18">
+        <v>47832.19</v>
+      </c>
+      <c r="AK367" s="19">
+        <v>-0.19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/purchase2526.xlsx
+++ b/data/purchase2526.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24026"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B711F563-01AF-4C8F-93DF-D43F557ED8F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF1C8426-9897-4D50-9595-022840104408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11194" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11811" uniqueCount="578">
   <si>
     <t>State Office</t>
   </si>
@@ -1681,6 +1681,78 @@
   <si>
     <t>7004635512</t>
   </si>
+  <si>
+    <t>1-1512490644267</t>
+  </si>
+  <si>
+    <t>7005246872</t>
+  </si>
+  <si>
+    <t>1-1517608024641</t>
+  </si>
+  <si>
+    <t>7005479851</t>
+  </si>
+  <si>
+    <t>SILVER</t>
+  </si>
+  <si>
+    <t>1-1511680649115</t>
+  </si>
+  <si>
+    <t>7005247020</t>
+  </si>
+  <si>
+    <t>1-1527384329268</t>
+  </si>
+  <si>
+    <t>7005983266</t>
+  </si>
+  <si>
+    <t>1-1528130320338</t>
+  </si>
+  <si>
+    <t>7006051811</t>
+  </si>
+  <si>
+    <t>1-1519808011560</t>
+  </si>
+  <si>
+    <t>7005572188</t>
+  </si>
+  <si>
+    <t>1-1522396572096</t>
+  </si>
+  <si>
+    <t>7005671253</t>
+  </si>
+  <si>
+    <t>1-1521029782020</t>
+  </si>
+  <si>
+    <t>7005607919</t>
+  </si>
+  <si>
+    <t>1-1528074073992</t>
+  </si>
+  <si>
+    <t>7006041514</t>
+  </si>
+  <si>
+    <t>1-1528100972648</t>
+  </si>
+  <si>
+    <t>7006034698</t>
+  </si>
+  <si>
+    <t>AS25FC4688</t>
+  </si>
+  <si>
+    <t>1-1519973316042</t>
+  </si>
+  <si>
+    <t>7005591490</t>
+  </si>
 </sst>
 </file>
 
@@ -2192,7 +2264,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AK621"/>
+  <dimension ref="A1:AK654"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.109375" customWidth="1"/>
@@ -70193,6 +70265,3633 @@
         <v>-0.44</v>
       </c>
     </row>
+    <row r="622" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A622" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B622" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C622" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D622" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E622" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F622" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G622" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H622" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="I622" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="J622" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="K622" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="L622" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="M622" s="14"/>
+      <c r="N622" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="O622" s="17">
+        <v>210</v>
+      </c>
+      <c r="P622" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q622" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R622" s="16" t="s">
+        <v>554</v>
+      </c>
+      <c r="S622" s="16" t="s">
+        <v>555</v>
+      </c>
+      <c r="T622" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="U622" s="18">
+        <v>46120</v>
+      </c>
+      <c r="V622" s="19">
+        <v>2</v>
+      </c>
+      <c r="W622" s="19">
+        <v>420</v>
+      </c>
+      <c r="X622" s="7"/>
+      <c r="Y622" s="19">
+        <v>171780</v>
+      </c>
+      <c r="Z622" s="7"/>
+      <c r="AA622" s="7"/>
+      <c r="AB622" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC622" s="19">
+        <v>-10306.799999999999</v>
+      </c>
+      <c r="AD622" s="19">
+        <v>-630</v>
+      </c>
+      <c r="AE622" s="19">
+        <v>-3216.86</v>
+      </c>
+      <c r="AF622" s="19">
+        <v>157626.34</v>
+      </c>
+      <c r="AG622" s="19">
+        <v>185999.08</v>
+      </c>
+      <c r="AH622" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI622" s="19">
+        <v>28372.74</v>
+      </c>
+      <c r="AJ622" s="19">
+        <v>185999.08</v>
+      </c>
+      <c r="AK622" s="20">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="623" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A623" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B623" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C623" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D623" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E623" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F623" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G623" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H623" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="I623" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="J623" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="K623" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="L623" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="M623" s="14"/>
+      <c r="N623" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="O623" s="17">
+        <v>210</v>
+      </c>
+      <c r="P623" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q623" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R623" s="16" t="s">
+        <v>556</v>
+      </c>
+      <c r="S623" s="16" t="s">
+        <v>557</v>
+      </c>
+      <c r="T623" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="U623" s="18">
+        <v>46127</v>
+      </c>
+      <c r="V623" s="19">
+        <v>2</v>
+      </c>
+      <c r="W623" s="19">
+        <v>420</v>
+      </c>
+      <c r="X623" s="7"/>
+      <c r="Y623" s="19">
+        <v>171780</v>
+      </c>
+      <c r="Z623" s="7"/>
+      <c r="AA623" s="7"/>
+      <c r="AB623" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC623" s="19">
+        <v>-10306.799999999999</v>
+      </c>
+      <c r="AD623" s="19">
+        <v>-630</v>
+      </c>
+      <c r="AE623" s="19">
+        <v>-3216.86</v>
+      </c>
+      <c r="AF623" s="19">
+        <v>157626.34</v>
+      </c>
+      <c r="AG623" s="19">
+        <v>185999.08</v>
+      </c>
+      <c r="AH623" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI623" s="19">
+        <v>28372.74</v>
+      </c>
+      <c r="AJ623" s="19">
+        <v>185999.08</v>
+      </c>
+      <c r="AK623" s="20">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="624" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A624" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B624" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C624" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D624" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E624" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F624" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G624" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H624" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="I624" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="J624" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="K624" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="L624" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="M624" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="N624" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="O624" s="17">
+        <v>14</v>
+      </c>
+      <c r="P624" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q624" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R624" s="16" t="s">
+        <v>556</v>
+      </c>
+      <c r="S624" s="16" t="s">
+        <v>557</v>
+      </c>
+      <c r="T624" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="U624" s="18">
+        <v>46127</v>
+      </c>
+      <c r="V624" s="19">
+        <v>15</v>
+      </c>
+      <c r="W624" s="19">
+        <v>210</v>
+      </c>
+      <c r="X624" s="19">
+        <v>96840</v>
+      </c>
+      <c r="Y624" s="19">
+        <v>62946</v>
+      </c>
+      <c r="Z624" s="19">
+        <v>71989.25</v>
+      </c>
+      <c r="AA624" s="19">
+        <v>-6090</v>
+      </c>
+      <c r="AB624" s="19">
+        <v>-4672.09</v>
+      </c>
+      <c r="AC624" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD624" s="19">
+        <v>-315</v>
+      </c>
+      <c r="AE624" s="19">
+        <v>-1218.24</v>
+      </c>
+      <c r="AF624" s="19">
+        <v>59693.919999999998</v>
+      </c>
+      <c r="AG624" s="19">
+        <v>70438.83</v>
+      </c>
+      <c r="AH624" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI624" s="19">
+        <v>10744.91</v>
+      </c>
+      <c r="AJ624" s="19">
+        <v>70438.83</v>
+      </c>
+      <c r="AK624" s="20">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="625" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A625" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B625" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C625" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D625" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E625" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F625" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G625" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H625" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="I625" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="J625" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="K625" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L625" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M625" s="14"/>
+      <c r="N625" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="O625" s="17">
+        <v>14</v>
+      </c>
+      <c r="P625" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q625" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R625" s="16" t="s">
+        <v>559</v>
+      </c>
+      <c r="S625" s="16" t="s">
+        <v>560</v>
+      </c>
+      <c r="T625" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="U625" s="18">
+        <v>46119</v>
+      </c>
+      <c r="V625" s="19">
+        <v>19</v>
+      </c>
+      <c r="W625" s="19">
+        <v>266</v>
+      </c>
+      <c r="X625" s="19">
+        <v>119700</v>
+      </c>
+      <c r="Y625" s="19">
+        <v>77805</v>
+      </c>
+      <c r="Z625" s="19">
+        <v>82724.09</v>
+      </c>
+      <c r="AA625" s="7"/>
+      <c r="AB625" s="19">
+        <v>-5368.78</v>
+      </c>
+      <c r="AC625" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD625" s="19">
+        <v>-399</v>
+      </c>
+      <c r="AE625" s="19">
+        <v>-1539.13</v>
+      </c>
+      <c r="AF625" s="19">
+        <v>75417.179999999993</v>
+      </c>
+      <c r="AG625" s="19">
+        <v>88992.27</v>
+      </c>
+      <c r="AH625" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI625" s="19">
+        <v>13575.09</v>
+      </c>
+      <c r="AJ625" s="19">
+        <v>88992.27</v>
+      </c>
+      <c r="AK625" s="20">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="626" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A626" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B626" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C626" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D626" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E626" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F626" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G626" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H626" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="I626" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="J626" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="K626" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L626" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M626" s="14"/>
+      <c r="N626" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="O626" s="17">
+        <v>14</v>
+      </c>
+      <c r="P626" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q626" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R626" s="16" t="s">
+        <v>554</v>
+      </c>
+      <c r="S626" s="16" t="s">
+        <v>555</v>
+      </c>
+      <c r="T626" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="U626" s="18">
+        <v>46120</v>
+      </c>
+      <c r="V626" s="19">
+        <v>11</v>
+      </c>
+      <c r="W626" s="19">
+        <v>154</v>
+      </c>
+      <c r="X626" s="19">
+        <v>69300</v>
+      </c>
+      <c r="Y626" s="19">
+        <v>45045</v>
+      </c>
+      <c r="Z626" s="19">
+        <v>47892.9</v>
+      </c>
+      <c r="AA626" s="7"/>
+      <c r="AB626" s="19">
+        <v>-3108.24</v>
+      </c>
+      <c r="AC626" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD626" s="19">
+        <v>-231</v>
+      </c>
+      <c r="AE626" s="19">
+        <v>-891.07</v>
+      </c>
+      <c r="AF626" s="19">
+        <v>43662.59</v>
+      </c>
+      <c r="AG626" s="19">
+        <v>51521.86</v>
+      </c>
+      <c r="AH626" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI626" s="19">
+        <v>7859.27</v>
+      </c>
+      <c r="AJ626" s="19">
+        <v>51521.86</v>
+      </c>
+      <c r="AK626" s="20">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="627" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A627" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B627" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C627" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D627" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E627" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F627" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G627" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H627" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="I627" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="J627" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="K627" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L627" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M627" s="14"/>
+      <c r="N627" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="O627" s="17">
+        <v>14</v>
+      </c>
+      <c r="P627" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q627" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R627" s="16" t="s">
+        <v>556</v>
+      </c>
+      <c r="S627" s="16" t="s">
+        <v>557</v>
+      </c>
+      <c r="T627" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="U627" s="18">
+        <v>46127</v>
+      </c>
+      <c r="V627" s="19">
+        <v>15</v>
+      </c>
+      <c r="W627" s="19">
+        <v>210</v>
+      </c>
+      <c r="X627" s="19">
+        <v>94500</v>
+      </c>
+      <c r="Y627" s="19">
+        <v>61425</v>
+      </c>
+      <c r="Z627" s="19">
+        <v>65308.5</v>
+      </c>
+      <c r="AA627" s="7"/>
+      <c r="AB627" s="19">
+        <v>-4238.51</v>
+      </c>
+      <c r="AC627" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD627" s="19">
+        <v>-315</v>
+      </c>
+      <c r="AE627" s="19">
+        <v>-1215.0999999999999</v>
+      </c>
+      <c r="AF627" s="19">
+        <v>59539.89</v>
+      </c>
+      <c r="AG627" s="19">
+        <v>70257.070000000007</v>
+      </c>
+      <c r="AH627" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI627" s="19">
+        <v>10717.18</v>
+      </c>
+      <c r="AJ627" s="19">
+        <v>70257.070000000007</v>
+      </c>
+      <c r="AK627" s="20">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="628" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A628" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B628" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C628" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D628" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E628" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F628" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G628" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H628" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="I628" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J628" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="K628" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L628" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M628" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="N628" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="O628" s="17">
+        <v>14</v>
+      </c>
+      <c r="P628" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q628" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R628" s="16" t="s">
+        <v>559</v>
+      </c>
+      <c r="S628" s="16" t="s">
+        <v>560</v>
+      </c>
+      <c r="T628" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="U628" s="18">
+        <v>46119</v>
+      </c>
+      <c r="V628" s="19">
+        <v>20</v>
+      </c>
+      <c r="W628" s="19">
+        <v>280</v>
+      </c>
+      <c r="X628" s="19">
+        <v>120160</v>
+      </c>
+      <c r="Y628" s="19">
+        <v>78104</v>
+      </c>
+      <c r="Z628" s="19">
+        <v>79440.240000000005</v>
+      </c>
+      <c r="AA628" s="19">
+        <v>-4200</v>
+      </c>
+      <c r="AB628" s="19">
+        <v>-5155.66</v>
+      </c>
+      <c r="AC628" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD628" s="19">
+        <v>-420</v>
+      </c>
+      <c r="AE628" s="19">
+        <v>-1393.29</v>
+      </c>
+      <c r="AF628" s="19">
+        <v>68271.289999999994</v>
+      </c>
+      <c r="AG628" s="19">
+        <v>80560.12</v>
+      </c>
+      <c r="AH628" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI628" s="19">
+        <v>12288.83</v>
+      </c>
+      <c r="AJ628" s="19">
+        <v>80560.12</v>
+      </c>
+      <c r="AK628" s="20">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="629" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A629" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B629" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C629" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D629" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E629" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F629" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G629" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H629" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="I629" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J629" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="K629" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L629" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M629" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="N629" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="O629" s="17">
+        <v>14</v>
+      </c>
+      <c r="P629" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q629" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R629" s="16" t="s">
+        <v>556</v>
+      </c>
+      <c r="S629" s="16" t="s">
+        <v>557</v>
+      </c>
+      <c r="T629" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="U629" s="18">
+        <v>46127</v>
+      </c>
+      <c r="V629" s="19">
+        <v>15</v>
+      </c>
+      <c r="W629" s="19">
+        <v>210</v>
+      </c>
+      <c r="X629" s="19">
+        <v>90120</v>
+      </c>
+      <c r="Y629" s="19">
+        <v>58578</v>
+      </c>
+      <c r="Z629" s="19">
+        <v>59580.18</v>
+      </c>
+      <c r="AA629" s="19">
+        <v>-3150</v>
+      </c>
+      <c r="AB629" s="19">
+        <v>-3866.74</v>
+      </c>
+      <c r="AC629" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD629" s="19">
+        <v>-315</v>
+      </c>
+      <c r="AE629" s="19">
+        <v>-1044.97</v>
+      </c>
+      <c r="AF629" s="19">
+        <v>51203.47</v>
+      </c>
+      <c r="AG629" s="19">
+        <v>60420.09</v>
+      </c>
+      <c r="AH629" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI629" s="19">
+        <v>9216.6200000000008</v>
+      </c>
+      <c r="AJ629" s="19">
+        <v>60420.09</v>
+      </c>
+      <c r="AK629" s="20">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="630" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A630" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B630" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C630" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D630" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E630" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F630" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G630" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H630" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="I630" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="J630" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="K630" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="L630" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M630" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="N630" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="O630" s="17">
+        <v>16</v>
+      </c>
+      <c r="P630" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q630" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R630" s="16" t="s">
+        <v>559</v>
+      </c>
+      <c r="S630" s="16" t="s">
+        <v>560</v>
+      </c>
+      <c r="T630" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="U630" s="18">
+        <v>46119</v>
+      </c>
+      <c r="V630" s="19">
+        <v>5</v>
+      </c>
+      <c r="W630" s="19">
+        <v>80</v>
+      </c>
+      <c r="X630" s="19">
+        <v>34400</v>
+      </c>
+      <c r="Y630" s="19">
+        <v>25480</v>
+      </c>
+      <c r="Z630" s="19">
+        <v>23322.1</v>
+      </c>
+      <c r="AA630" s="7"/>
+      <c r="AB630" s="19">
+        <v>-1513.6</v>
+      </c>
+      <c r="AC630" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD630" s="19">
+        <v>-120</v>
+      </c>
+      <c r="AE630" s="19">
+        <v>-433.77</v>
+      </c>
+      <c r="AF630" s="19">
+        <v>21254.73</v>
+      </c>
+      <c r="AG630" s="19">
+        <v>25080.58</v>
+      </c>
+      <c r="AH630" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI630" s="19">
+        <v>3825.85</v>
+      </c>
+      <c r="AJ630" s="19">
+        <v>25080.58</v>
+      </c>
+      <c r="AK630" s="20">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="631" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A631" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B631" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C631" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D631" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E631" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F631" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G631" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H631" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="I631" s="16" t="s">
+        <v>454</v>
+      </c>
+      <c r="J631" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="K631" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="L631" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="M631" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="N631" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="O631" s="17">
+        <v>12</v>
+      </c>
+      <c r="P631" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q631" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R631" s="16" t="s">
+        <v>561</v>
+      </c>
+      <c r="S631" s="16" t="s">
+        <v>562</v>
+      </c>
+      <c r="T631" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="U631" s="18">
+        <v>46141</v>
+      </c>
+      <c r="V631" s="19">
+        <v>100</v>
+      </c>
+      <c r="W631" s="19">
+        <v>1200</v>
+      </c>
+      <c r="X631" s="19">
+        <v>406800</v>
+      </c>
+      <c r="Y631" s="19">
+        <v>264420</v>
+      </c>
+      <c r="Z631" s="19">
+        <v>257408.59</v>
+      </c>
+      <c r="AA631" s="19">
+        <v>-14400</v>
+      </c>
+      <c r="AB631" s="19">
+        <v>-16705.77</v>
+      </c>
+      <c r="AC631" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD631" s="7"/>
+      <c r="AE631" s="19">
+        <v>-4526.0600000000004</v>
+      </c>
+      <c r="AF631" s="19">
+        <v>221776.76</v>
+      </c>
+      <c r="AG631" s="19">
+        <v>261696.58</v>
+      </c>
+      <c r="AH631" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI631" s="19">
+        <v>39919.82</v>
+      </c>
+      <c r="AJ631" s="19">
+        <v>261696.58</v>
+      </c>
+      <c r="AK631" s="20">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="632" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A632" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B632" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C632" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D632" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E632" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F632" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G632" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H632" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="I632" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="J632" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="K632" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="L632" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="M632" s="14"/>
+      <c r="N632" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="O632" s="17">
+        <v>12</v>
+      </c>
+      <c r="P632" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q632" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R632" s="16" t="s">
+        <v>556</v>
+      </c>
+      <c r="S632" s="16" t="s">
+        <v>557</v>
+      </c>
+      <c r="T632" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="U632" s="18">
+        <v>46127</v>
+      </c>
+      <c r="V632" s="19">
+        <v>20</v>
+      </c>
+      <c r="W632" s="19">
+        <v>240</v>
+      </c>
+      <c r="X632" s="19">
+        <v>86160</v>
+      </c>
+      <c r="Y632" s="19">
+        <v>56004</v>
+      </c>
+      <c r="Z632" s="19">
+        <v>58118.73</v>
+      </c>
+      <c r="AA632" s="19">
+        <v>-1920</v>
+      </c>
+      <c r="AB632" s="19">
+        <v>-3771.9</v>
+      </c>
+      <c r="AC632" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD632" s="19">
+        <v>-360</v>
+      </c>
+      <c r="AE632" s="19">
+        <v>-1041.3399999999999</v>
+      </c>
+      <c r="AF632" s="19">
+        <v>51025.49</v>
+      </c>
+      <c r="AG632" s="19">
+        <v>60210.080000000002</v>
+      </c>
+      <c r="AH632" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI632" s="19">
+        <v>9184.59</v>
+      </c>
+      <c r="AJ632" s="19">
+        <v>60210.080000000002</v>
+      </c>
+      <c r="AK632" s="20">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="633" spans="1:37" ht="40.799999999999997" x14ac:dyDescent="0.3">
+      <c r="A633" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B633" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C633" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D633" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E633" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F633" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G633" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H633" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="I633" s="16" t="s">
+        <v>420</v>
+      </c>
+      <c r="J633" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="K633" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="L633" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="M633" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="N633" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="O633" s="17">
+        <v>20</v>
+      </c>
+      <c r="P633" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q633" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R633" s="16" t="s">
+        <v>561</v>
+      </c>
+      <c r="S633" s="16" t="s">
+        <v>562</v>
+      </c>
+      <c r="T633" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="U633" s="18">
+        <v>46141</v>
+      </c>
+      <c r="V633" s="19">
+        <v>5</v>
+      </c>
+      <c r="W633" s="19">
+        <v>100</v>
+      </c>
+      <c r="X633" s="19">
+        <v>31600</v>
+      </c>
+      <c r="Y633" s="19">
+        <v>22490</v>
+      </c>
+      <c r="Z633" s="19">
+        <v>20913.63</v>
+      </c>
+      <c r="AA633" s="19">
+        <v>-1900</v>
+      </c>
+      <c r="AB633" s="19">
+        <v>-1480.68</v>
+      </c>
+      <c r="AC633" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD633" s="7"/>
+      <c r="AE633" s="19">
+        <v>-350.66</v>
+      </c>
+      <c r="AF633" s="19">
+        <v>17182.29</v>
+      </c>
+      <c r="AG633" s="19">
+        <v>20275.099999999999</v>
+      </c>
+      <c r="AH633" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI633" s="19">
+        <v>3092.81</v>
+      </c>
+      <c r="AJ633" s="19">
+        <v>20275.099999999999</v>
+      </c>
+      <c r="AK633" s="20">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="634" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A634" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B634" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C634" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D634" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E634" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F634" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G634" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H634" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="I634" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="J634" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="K634" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="L634" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="M634" s="14"/>
+      <c r="N634" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="O634" s="17">
+        <v>210</v>
+      </c>
+      <c r="P634" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q634" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R634" s="16" t="s">
+        <v>563</v>
+      </c>
+      <c r="S634" s="16" t="s">
+        <v>564</v>
+      </c>
+      <c r="T634" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="U634" s="18">
+        <v>46142</v>
+      </c>
+      <c r="V634" s="19">
+        <v>4</v>
+      </c>
+      <c r="W634" s="19">
+        <v>840</v>
+      </c>
+      <c r="X634" s="7"/>
+      <c r="Y634" s="19">
+        <v>343560</v>
+      </c>
+      <c r="Z634" s="7"/>
+      <c r="AA634" s="7"/>
+      <c r="AB634" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC634" s="19">
+        <v>-20613.599999999999</v>
+      </c>
+      <c r="AD634" s="7"/>
+      <c r="AE634" s="19">
+        <v>-6458.93</v>
+      </c>
+      <c r="AF634" s="19">
+        <v>316487.46999999997</v>
+      </c>
+      <c r="AG634" s="19">
+        <v>373455.21</v>
+      </c>
+      <c r="AH634" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI634" s="19">
+        <v>56967.74</v>
+      </c>
+      <c r="AJ634" s="19">
+        <v>373455.21</v>
+      </c>
+      <c r="AK634" s="20">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="635" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A635" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B635" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C635" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D635" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E635" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F635" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G635" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H635" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="I635" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="J635" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="K635" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="L635" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="M635" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="N635" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="O635" s="17">
+        <v>14</v>
+      </c>
+      <c r="P635" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q635" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R635" s="16" t="s">
+        <v>565</v>
+      </c>
+      <c r="S635" s="16" t="s">
+        <v>566</v>
+      </c>
+      <c r="T635" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="U635" s="18">
+        <v>46130</v>
+      </c>
+      <c r="V635" s="19">
+        <v>30</v>
+      </c>
+      <c r="W635" s="19">
+        <v>420</v>
+      </c>
+      <c r="X635" s="19">
+        <v>193680</v>
+      </c>
+      <c r="Y635" s="19">
+        <v>125892</v>
+      </c>
+      <c r="Z635" s="19">
+        <v>143978.5</v>
+      </c>
+      <c r="AA635" s="19">
+        <v>-12180</v>
+      </c>
+      <c r="AB635" s="19">
+        <v>-9344.18</v>
+      </c>
+      <c r="AC635" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD635" s="19">
+        <v>-420</v>
+      </c>
+      <c r="AE635" s="19">
+        <v>-2440.69</v>
+      </c>
+      <c r="AF635" s="19">
+        <v>119593.63</v>
+      </c>
+      <c r="AG635" s="19">
+        <v>141120.48000000001</v>
+      </c>
+      <c r="AH635" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI635" s="19">
+        <v>21526.85</v>
+      </c>
+      <c r="AJ635" s="19">
+        <v>141120.48000000001</v>
+      </c>
+      <c r="AK635" s="20">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="636" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A636" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B636" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C636" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D636" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E636" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F636" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G636" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H636" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="I636" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="J636" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="K636" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L636" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M636" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="N636" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="O636" s="17">
+        <v>210</v>
+      </c>
+      <c r="P636" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q636" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R636" s="16" t="s">
+        <v>565</v>
+      </c>
+      <c r="S636" s="16" t="s">
+        <v>566</v>
+      </c>
+      <c r="T636" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="U636" s="18">
+        <v>46130</v>
+      </c>
+      <c r="V636" s="19">
+        <v>2</v>
+      </c>
+      <c r="W636" s="19">
+        <v>420</v>
+      </c>
+      <c r="X636" s="7"/>
+      <c r="Y636" s="19">
+        <v>136500</v>
+      </c>
+      <c r="Z636" s="7"/>
+      <c r="AA636" s="7"/>
+      <c r="AB636" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC636" s="19">
+        <v>-7507.5</v>
+      </c>
+      <c r="AD636" s="19">
+        <v>-420</v>
+      </c>
+      <c r="AE636" s="19">
+        <v>-2571.4499999999998</v>
+      </c>
+      <c r="AF636" s="19">
+        <v>126001.05</v>
+      </c>
+      <c r="AG636" s="19">
+        <v>148681.24</v>
+      </c>
+      <c r="AH636" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI636" s="19">
+        <v>22680.19</v>
+      </c>
+      <c r="AJ636" s="19">
+        <v>148681.24</v>
+      </c>
+      <c r="AK636" s="20">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="637" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A637" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B637" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C637" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D637" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E637" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F637" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G637" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H637" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="I637" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="J637" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="K637" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="L637" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="M637" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="N637" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="O637" s="17">
+        <v>14</v>
+      </c>
+      <c r="P637" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q637" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R637" s="16" t="s">
+        <v>565</v>
+      </c>
+      <c r="S637" s="16" t="s">
+        <v>566</v>
+      </c>
+      <c r="T637" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="U637" s="18">
+        <v>46130</v>
+      </c>
+      <c r="V637" s="19">
+        <v>15</v>
+      </c>
+      <c r="W637" s="19">
+        <v>210</v>
+      </c>
+      <c r="X637" s="19">
+        <v>75420</v>
+      </c>
+      <c r="Y637" s="19">
+        <v>49023</v>
+      </c>
+      <c r="Z637" s="19">
+        <v>50892.02</v>
+      </c>
+      <c r="AA637" s="19">
+        <v>-1680</v>
+      </c>
+      <c r="AB637" s="19">
+        <v>-3302.88</v>
+      </c>
+      <c r="AC637" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD637" s="19">
+        <v>-210</v>
+      </c>
+      <c r="AE637" s="19">
+        <v>-913.98</v>
+      </c>
+      <c r="AF637" s="19">
+        <v>44785.16</v>
+      </c>
+      <c r="AG637" s="19">
+        <v>52846.49</v>
+      </c>
+      <c r="AH637" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI637" s="19">
+        <v>8061.33</v>
+      </c>
+      <c r="AJ637" s="19">
+        <v>52846.49</v>
+      </c>
+      <c r="AK637" s="20">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="638" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A638" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B638" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C638" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D638" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E638" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F638" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G638" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H638" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="I638" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="J638" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="K638" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="L638" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="M638" s="14"/>
+      <c r="N638" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="O638" s="17">
+        <v>210</v>
+      </c>
+      <c r="P638" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q638" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R638" s="16" t="s">
+        <v>567</v>
+      </c>
+      <c r="S638" s="16" t="s">
+        <v>568</v>
+      </c>
+      <c r="T638" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="U638" s="18">
+        <v>46134</v>
+      </c>
+      <c r="V638" s="19">
+        <v>1</v>
+      </c>
+      <c r="W638" s="19">
+        <v>210</v>
+      </c>
+      <c r="X638" s="7"/>
+      <c r="Y638" s="19">
+        <v>85890</v>
+      </c>
+      <c r="Z638" s="7"/>
+      <c r="AA638" s="7"/>
+      <c r="AB638" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC638" s="19">
+        <v>-5153.3999999999996</v>
+      </c>
+      <c r="AD638" s="19">
+        <v>-105</v>
+      </c>
+      <c r="AE638" s="19">
+        <v>-1612.63</v>
+      </c>
+      <c r="AF638" s="19">
+        <v>79018.97</v>
+      </c>
+      <c r="AG638" s="19">
+        <v>93242.38</v>
+      </c>
+      <c r="AH638" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI638" s="19">
+        <v>14223.41</v>
+      </c>
+      <c r="AJ638" s="19">
+        <v>93242.38</v>
+      </c>
+      <c r="AK638" s="20">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="639" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A639" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B639" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C639" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D639" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E639" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F639" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G639" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H639" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="I639" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="J639" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="K639" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L639" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M639" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="N639" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="O639" s="17">
+        <v>210</v>
+      </c>
+      <c r="P639" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q639" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R639" s="16" t="s">
+        <v>567</v>
+      </c>
+      <c r="S639" s="16" t="s">
+        <v>568</v>
+      </c>
+      <c r="T639" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="U639" s="18">
+        <v>46134</v>
+      </c>
+      <c r="V639" s="19">
+        <v>1</v>
+      </c>
+      <c r="W639" s="19">
+        <v>210</v>
+      </c>
+      <c r="X639" s="7"/>
+      <c r="Y639" s="19">
+        <v>68250</v>
+      </c>
+      <c r="Z639" s="7"/>
+      <c r="AA639" s="7"/>
+      <c r="AB639" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC639" s="19">
+        <v>-3753.75</v>
+      </c>
+      <c r="AD639" s="19">
+        <v>-105</v>
+      </c>
+      <c r="AE639" s="19">
+        <v>-1287.83</v>
+      </c>
+      <c r="AF639" s="19">
+        <v>63103.42</v>
+      </c>
+      <c r="AG639" s="19">
+        <v>74462.039999999994</v>
+      </c>
+      <c r="AH639" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI639" s="19">
+        <v>11358.62</v>
+      </c>
+      <c r="AJ639" s="19">
+        <v>74462.039999999994</v>
+      </c>
+      <c r="AK639" s="20">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="640" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A640" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B640" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C640" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D640" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E640" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F640" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G640" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H640" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="I640" s="16" t="s">
+        <v>454</v>
+      </c>
+      <c r="J640" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="K640" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="L640" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="M640" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="N640" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="O640" s="17">
+        <v>12</v>
+      </c>
+      <c r="P640" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q640" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R640" s="16" t="s">
+        <v>569</v>
+      </c>
+      <c r="S640" s="16" t="s">
+        <v>570</v>
+      </c>
+      <c r="T640" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="U640" s="18">
+        <v>46132</v>
+      </c>
+      <c r="V640" s="19">
+        <v>85</v>
+      </c>
+      <c r="W640" s="19">
+        <v>1020</v>
+      </c>
+      <c r="X640" s="19">
+        <v>345780</v>
+      </c>
+      <c r="Y640" s="19">
+        <v>224757</v>
+      </c>
+      <c r="Z640" s="19">
+        <v>218797.3</v>
+      </c>
+      <c r="AA640" s="19">
+        <v>-12240</v>
+      </c>
+      <c r="AB640" s="19">
+        <v>-14199.9</v>
+      </c>
+      <c r="AC640" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD640" s="19">
+        <v>-1020</v>
+      </c>
+      <c r="AE640" s="19">
+        <v>-3826.75</v>
+      </c>
+      <c r="AF640" s="19">
+        <v>187510.65</v>
+      </c>
+      <c r="AG640" s="19">
+        <v>221262.57</v>
+      </c>
+      <c r="AH640" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI640" s="19">
+        <v>33751.919999999998</v>
+      </c>
+      <c r="AJ640" s="19">
+        <v>221262.57</v>
+      </c>
+      <c r="AK640" s="20">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="641" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A641" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B641" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C641" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D641" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E641" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F641" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G641" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H641" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="I641" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="J641" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="K641" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="L641" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="M641" s="14"/>
+      <c r="N641" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="O641" s="17">
+        <v>20</v>
+      </c>
+      <c r="P641" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q641" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R641" s="16" t="s">
+        <v>571</v>
+      </c>
+      <c r="S641" s="16" t="s">
+        <v>572</v>
+      </c>
+      <c r="T641" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="U641" s="18">
+        <v>46142</v>
+      </c>
+      <c r="V641" s="19">
+        <v>4</v>
+      </c>
+      <c r="W641" s="19">
+        <v>80</v>
+      </c>
+      <c r="X641" s="19">
+        <v>34000</v>
+      </c>
+      <c r="Y641" s="19">
+        <v>22100</v>
+      </c>
+      <c r="Z641" s="19">
+        <v>21259.86</v>
+      </c>
+      <c r="AA641" s="19">
+        <v>-240</v>
+      </c>
+      <c r="AB641" s="19">
+        <v>-1505.19</v>
+      </c>
+      <c r="AC641" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD641" s="7"/>
+      <c r="AE641" s="19">
+        <v>-390.29</v>
+      </c>
+      <c r="AF641" s="19">
+        <v>19124.38</v>
+      </c>
+      <c r="AG641" s="19">
+        <v>22566.77</v>
+      </c>
+      <c r="AH641" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI641" s="19">
+        <v>3442.39</v>
+      </c>
+      <c r="AJ641" s="19">
+        <v>22566.77</v>
+      </c>
+      <c r="AK641" s="20">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="642" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A642" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B642" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C642" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D642" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E642" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F642" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G642" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H642" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="I642" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="J642" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="K642" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="L642" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="M642" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="N642" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="O642" s="17">
+        <v>5</v>
+      </c>
+      <c r="P642" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q642" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R642" s="16" t="s">
+        <v>571</v>
+      </c>
+      <c r="S642" s="16" t="s">
+        <v>572</v>
+      </c>
+      <c r="T642" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="U642" s="18">
+        <v>46142</v>
+      </c>
+      <c r="V642" s="19">
+        <v>5</v>
+      </c>
+      <c r="W642" s="19">
+        <v>25</v>
+      </c>
+      <c r="X642" s="19">
+        <v>11000</v>
+      </c>
+      <c r="Y642" s="19">
+        <v>7898</v>
+      </c>
+      <c r="Z642" s="19">
+        <v>7453.45</v>
+      </c>
+      <c r="AA642" s="7"/>
+      <c r="AB642" s="19">
+        <v>-527.70000000000005</v>
+      </c>
+      <c r="AC642" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD642" s="7"/>
+      <c r="AE642" s="19">
+        <v>-138.52000000000001</v>
+      </c>
+      <c r="AF642" s="19">
+        <v>6787.23</v>
+      </c>
+      <c r="AG642" s="19">
+        <v>8008.93</v>
+      </c>
+      <c r="AH642" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI642" s="19">
+        <v>1221.7</v>
+      </c>
+      <c r="AJ642" s="19">
+        <v>8008.93</v>
+      </c>
+      <c r="AK642" s="20">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="643" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A643" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B643" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C643" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D643" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E643" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F643" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G643" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H643" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="I643" s="16" t="s">
+        <v>425</v>
+      </c>
+      <c r="J643" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="K643" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="L643" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="M643" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="N643" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="O643" s="17">
+        <v>14</v>
+      </c>
+      <c r="P643" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q643" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R643" s="16" t="s">
+        <v>571</v>
+      </c>
+      <c r="S643" s="16" t="s">
+        <v>572</v>
+      </c>
+      <c r="T643" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="U643" s="18">
+        <v>46142</v>
+      </c>
+      <c r="V643" s="19">
+        <v>3</v>
+      </c>
+      <c r="W643" s="19">
+        <v>42</v>
+      </c>
+      <c r="X643" s="19">
+        <v>24060</v>
+      </c>
+      <c r="Y643" s="19">
+        <v>16871.400000000001</v>
+      </c>
+      <c r="Z643" s="19">
+        <v>13233.24</v>
+      </c>
+      <c r="AA643" s="19">
+        <v>-1638</v>
+      </c>
+      <c r="AB643" s="19">
+        <v>-1171.1400000000001</v>
+      </c>
+      <c r="AC643" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD643" s="7"/>
+      <c r="AE643" s="19">
+        <v>-208.48</v>
+      </c>
+      <c r="AF643" s="19">
+        <v>10215.620000000001</v>
+      </c>
+      <c r="AG643" s="19">
+        <v>12054.43</v>
+      </c>
+      <c r="AH643" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI643" s="19">
+        <v>1838.81</v>
+      </c>
+      <c r="AJ643" s="19">
+        <v>12054.43</v>
+      </c>
+      <c r="AK643" s="20">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="644" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A644" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B644" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C644" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D644" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E644" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F644" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G644" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H644" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="I644" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="J644" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="K644" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="L644" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="M644" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="N644" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="O644" s="17">
+        <v>20</v>
+      </c>
+      <c r="P644" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q644" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R644" s="16" t="s">
+        <v>571</v>
+      </c>
+      <c r="S644" s="16" t="s">
+        <v>572</v>
+      </c>
+      <c r="T644" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="U644" s="18">
+        <v>46142</v>
+      </c>
+      <c r="V644" s="19">
+        <v>5</v>
+      </c>
+      <c r="W644" s="19">
+        <v>100</v>
+      </c>
+      <c r="X644" s="19">
+        <v>39400</v>
+      </c>
+      <c r="Y644" s="19">
+        <v>25610</v>
+      </c>
+      <c r="Z644" s="19">
+        <v>27076.89</v>
+      </c>
+      <c r="AA644" s="19">
+        <v>-1900</v>
+      </c>
+      <c r="AB644" s="19">
+        <v>-1917.04</v>
+      </c>
+      <c r="AC644" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD644" s="7"/>
+      <c r="AE644" s="19">
+        <v>-465.2</v>
+      </c>
+      <c r="AF644" s="19">
+        <v>22794.65</v>
+      </c>
+      <c r="AG644" s="19">
+        <v>26897.69</v>
+      </c>
+      <c r="AH644" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI644" s="19">
+        <v>4103.04</v>
+      </c>
+      <c r="AJ644" s="19">
+        <v>26897.69</v>
+      </c>
+      <c r="AK644" s="20">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="645" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A645" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B645" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C645" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D645" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E645" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F645" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G645" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H645" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="I645" s="16" t="s">
+        <v>410</v>
+      </c>
+      <c r="J645" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="K645" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="L645" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="M645" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="N645" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="O645" s="17">
+        <v>15</v>
+      </c>
+      <c r="P645" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q645" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R645" s="16" t="s">
+        <v>571</v>
+      </c>
+      <c r="S645" s="16" t="s">
+        <v>572</v>
+      </c>
+      <c r="T645" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="U645" s="18">
+        <v>46142</v>
+      </c>
+      <c r="V645" s="19">
+        <v>2</v>
+      </c>
+      <c r="W645" s="19">
+        <v>30</v>
+      </c>
+      <c r="X645" s="19">
+        <v>10050</v>
+      </c>
+      <c r="Y645" s="19">
+        <v>7410</v>
+      </c>
+      <c r="Z645" s="19">
+        <v>6723.72</v>
+      </c>
+      <c r="AA645" s="19">
+        <v>-600</v>
+      </c>
+      <c r="AB645" s="19">
+        <v>-476.04</v>
+      </c>
+      <c r="AC645" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD645" s="7"/>
+      <c r="AE645" s="19">
+        <v>-112.95</v>
+      </c>
+      <c r="AF645" s="19">
+        <v>5534.73</v>
+      </c>
+      <c r="AG645" s="19">
+        <v>6530.98</v>
+      </c>
+      <c r="AH645" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI645" s="19">
+        <v>996.25</v>
+      </c>
+      <c r="AJ645" s="19">
+        <v>6530.98</v>
+      </c>
+      <c r="AK645" s="20">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="646" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A646" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B646" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C646" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D646" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E646" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F646" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G646" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H646" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="I646" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="J646" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="K646" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="L646" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="M646" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="N646" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="O646" s="17">
+        <v>20</v>
+      </c>
+      <c r="P646" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q646" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R646" s="16" t="s">
+        <v>571</v>
+      </c>
+      <c r="S646" s="16" t="s">
+        <v>572</v>
+      </c>
+      <c r="T646" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="U646" s="18">
+        <v>46142</v>
+      </c>
+      <c r="V646" s="19">
+        <v>5</v>
+      </c>
+      <c r="W646" s="19">
+        <v>100</v>
+      </c>
+      <c r="X646" s="19">
+        <v>35500</v>
+      </c>
+      <c r="Y646" s="19">
+        <v>26000</v>
+      </c>
+      <c r="Z646" s="19">
+        <v>23515.21</v>
+      </c>
+      <c r="AA646" s="19">
+        <v>-300</v>
+      </c>
+      <c r="AB646" s="19">
+        <v>-277.48</v>
+      </c>
+      <c r="AC646" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD646" s="7"/>
+      <c r="AE646" s="19">
+        <v>-458.75</v>
+      </c>
+      <c r="AF646" s="19">
+        <v>22478.98</v>
+      </c>
+      <c r="AG646" s="19">
+        <v>26525.200000000001</v>
+      </c>
+      <c r="AH646" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI646" s="19">
+        <v>4046.22</v>
+      </c>
+      <c r="AJ646" s="19">
+        <v>26525.200000000001</v>
+      </c>
+      <c r="AK646" s="20">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="647" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A647" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B647" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C647" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D647" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E647" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F647" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G647" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H647" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="I647" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="J647" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="K647" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="L647" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="M647" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="N647" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="O647" s="17">
+        <v>20</v>
+      </c>
+      <c r="P647" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q647" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R647" s="16" t="s">
+        <v>571</v>
+      </c>
+      <c r="S647" s="16" t="s">
+        <v>572</v>
+      </c>
+      <c r="T647" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="U647" s="18">
+        <v>46142</v>
+      </c>
+      <c r="V647" s="19">
+        <v>10</v>
+      </c>
+      <c r="W647" s="19">
+        <v>200</v>
+      </c>
+      <c r="X647" s="19">
+        <v>69400</v>
+      </c>
+      <c r="Y647" s="19">
+        <v>45110</v>
+      </c>
+      <c r="Z647" s="19">
+        <v>47252.71</v>
+      </c>
+      <c r="AA647" s="19">
+        <v>-800</v>
+      </c>
+      <c r="AB647" s="19">
+        <v>-3345.48</v>
+      </c>
+      <c r="AC647" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD647" s="7"/>
+      <c r="AE647" s="19">
+        <v>-862.14</v>
+      </c>
+      <c r="AF647" s="19">
+        <v>42245.09</v>
+      </c>
+      <c r="AG647" s="19">
+        <v>49849.21</v>
+      </c>
+      <c r="AH647" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI647" s="19">
+        <v>7604.12</v>
+      </c>
+      <c r="AJ647" s="19">
+        <v>49849.21</v>
+      </c>
+      <c r="AK647" s="20">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="648" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A648" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B648" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C648" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D648" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E648" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F648" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G648" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H648" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="I648" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="J648" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="K648" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="L648" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="M648" s="14"/>
+      <c r="N648" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="O648" s="17">
+        <v>10</v>
+      </c>
+      <c r="P648" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q648" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R648" s="16" t="s">
+        <v>571</v>
+      </c>
+      <c r="S648" s="16" t="s">
+        <v>572</v>
+      </c>
+      <c r="T648" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="U648" s="18">
+        <v>46142</v>
+      </c>
+      <c r="V648" s="19">
+        <v>5</v>
+      </c>
+      <c r="W648" s="19">
+        <v>50</v>
+      </c>
+      <c r="X648" s="19">
+        <v>15200</v>
+      </c>
+      <c r="Y648" s="19">
+        <v>10855</v>
+      </c>
+      <c r="Z648" s="19">
+        <v>10264.93</v>
+      </c>
+      <c r="AA648" s="19">
+        <v>-950</v>
+      </c>
+      <c r="AB648" s="19">
+        <v>-726.75</v>
+      </c>
+      <c r="AC648" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD648" s="7"/>
+      <c r="AE648" s="19">
+        <v>-171.76</v>
+      </c>
+      <c r="AF648" s="19">
+        <v>8416.42</v>
+      </c>
+      <c r="AG648" s="19">
+        <v>9931.3799999999992</v>
+      </c>
+      <c r="AH648" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI648" s="19">
+        <v>1514.96</v>
+      </c>
+      <c r="AJ648" s="19">
+        <v>9931.3799999999992</v>
+      </c>
+      <c r="AK648" s="20">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="649" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A649" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B649" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C649" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D649" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E649" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F649" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G649" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H649" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="I649" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="J649" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="K649" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="L649" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="M649" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="N649" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="O649" s="17">
+        <v>10</v>
+      </c>
+      <c r="P649" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q649" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R649" s="16" t="s">
+        <v>571</v>
+      </c>
+      <c r="S649" s="16" t="s">
+        <v>572</v>
+      </c>
+      <c r="T649" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="U649" s="18">
+        <v>46142</v>
+      </c>
+      <c r="V649" s="19">
+        <v>5</v>
+      </c>
+      <c r="W649" s="19">
+        <v>50</v>
+      </c>
+      <c r="X649" s="19">
+        <v>19800</v>
+      </c>
+      <c r="Y649" s="19">
+        <v>14365</v>
+      </c>
+      <c r="Z649" s="19">
+        <v>12587.3</v>
+      </c>
+      <c r="AA649" s="19">
+        <v>-450</v>
+      </c>
+      <c r="AB649" s="19">
+        <v>-891.18</v>
+      </c>
+      <c r="AC649" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD649" s="7"/>
+      <c r="AE649" s="19">
+        <v>-224.92</v>
+      </c>
+      <c r="AF649" s="19">
+        <v>11021.2</v>
+      </c>
+      <c r="AG649" s="19">
+        <v>13005.02</v>
+      </c>
+      <c r="AH649" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI649" s="19">
+        <v>1983.82</v>
+      </c>
+      <c r="AJ649" s="19">
+        <v>13005.02</v>
+      </c>
+      <c r="AK649" s="20">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="650" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A650" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B650" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C650" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D650" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E650" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F650" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G650" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H650" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="I650" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="J650" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="K650" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="L650" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="M650" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="N650" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="O650" s="17">
+        <v>20</v>
+      </c>
+      <c r="P650" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q650" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R650" s="16" t="s">
+        <v>571</v>
+      </c>
+      <c r="S650" s="16" t="s">
+        <v>572</v>
+      </c>
+      <c r="T650" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="U650" s="18">
+        <v>46142</v>
+      </c>
+      <c r="V650" s="19">
+        <v>5</v>
+      </c>
+      <c r="W650" s="19">
+        <v>100</v>
+      </c>
+      <c r="X650" s="19">
+        <v>42000</v>
+      </c>
+      <c r="Y650" s="19">
+        <v>27300</v>
+      </c>
+      <c r="Z650" s="19">
+        <v>28186.35</v>
+      </c>
+      <c r="AA650" s="19">
+        <v>-900</v>
+      </c>
+      <c r="AB650" s="19">
+        <v>-1995.59</v>
+      </c>
+      <c r="AC650" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD650" s="7"/>
+      <c r="AE650" s="19">
+        <v>-505.82</v>
+      </c>
+      <c r="AF650" s="19">
+        <v>24784.94</v>
+      </c>
+      <c r="AG650" s="19">
+        <v>29246.23</v>
+      </c>
+      <c r="AH650" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI650" s="19">
+        <v>4461.29</v>
+      </c>
+      <c r="AJ650" s="19">
+        <v>29246.23</v>
+      </c>
+      <c r="AK650" s="20">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="651" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A651" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B651" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C651" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D651" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E651" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="F651" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G651" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H651" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="I651" s="16" t="s">
+        <v>440</v>
+      </c>
+      <c r="J651" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="K651" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="L651" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="M651" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="N651" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="O651" s="17">
+        <v>20</v>
+      </c>
+      <c r="P651" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q651" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R651" s="16" t="s">
+        <v>573</v>
+      </c>
+      <c r="S651" s="16" t="s">
+        <v>574</v>
+      </c>
+      <c r="T651" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="U651" s="18">
+        <v>46142</v>
+      </c>
+      <c r="V651" s="19">
+        <v>1</v>
+      </c>
+      <c r="W651" s="19">
+        <v>20</v>
+      </c>
+      <c r="X651" s="19">
+        <v>8200</v>
+      </c>
+      <c r="Y651" s="19">
+        <v>5720</v>
+      </c>
+      <c r="Z651" s="19">
+        <v>5528.35</v>
+      </c>
+      <c r="AA651" s="19">
+        <v>-680</v>
+      </c>
+      <c r="AB651" s="19">
+        <v>-489.26</v>
+      </c>
+      <c r="AC651" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD651" s="7"/>
+      <c r="AE651" s="19">
+        <v>-87.18</v>
+      </c>
+      <c r="AF651" s="19">
+        <v>4271.91</v>
+      </c>
+      <c r="AG651" s="19">
+        <v>5040.8500000000004</v>
+      </c>
+      <c r="AH651" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI651" s="19">
+        <v>768.94</v>
+      </c>
+      <c r="AJ651" s="19">
+        <v>5040.8500000000004</v>
+      </c>
+      <c r="AK651" s="20">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="652" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A652" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B652" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C652" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D652" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E652" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="F652" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G652" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H652" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="I652" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="J652" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="K652" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="L652" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="M652" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="N652" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="O652" s="17">
+        <v>20</v>
+      </c>
+      <c r="P652" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q652" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R652" s="16" t="s">
+        <v>573</v>
+      </c>
+      <c r="S652" s="16" t="s">
+        <v>574</v>
+      </c>
+      <c r="T652" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="U652" s="18">
+        <v>46142</v>
+      </c>
+      <c r="V652" s="19">
+        <v>32</v>
+      </c>
+      <c r="W652" s="19">
+        <v>640</v>
+      </c>
+      <c r="X652" s="19">
+        <v>199680</v>
+      </c>
+      <c r="Y652" s="19">
+        <v>148928</v>
+      </c>
+      <c r="Z652" s="19">
+        <v>128846.42</v>
+      </c>
+      <c r="AA652" s="7"/>
+      <c r="AB652" s="19">
+        <v>-9122.2999999999993</v>
+      </c>
+      <c r="AC652" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD652" s="7"/>
+      <c r="AE652" s="19">
+        <v>-2394.48</v>
+      </c>
+      <c r="AF652" s="19">
+        <v>117329.64</v>
+      </c>
+      <c r="AG652" s="19">
+        <v>138448.98000000001</v>
+      </c>
+      <c r="AH652" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI652" s="19">
+        <v>21119.34</v>
+      </c>
+      <c r="AJ652" s="19">
+        <v>138448.98000000001</v>
+      </c>
+      <c r="AK652" s="20">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="653" spans="1:37" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A653" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B653" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C653" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D653" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E653" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="F653" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G653" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H653" s="16" t="s">
+        <v>575</v>
+      </c>
+      <c r="I653" s="16" t="s">
+        <v>349</v>
+      </c>
+      <c r="J653" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="K653" s="16" t="s">
+        <v>350</v>
+      </c>
+      <c r="L653" s="16" t="s">
+        <v>351</v>
+      </c>
+      <c r="M653" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="N653" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="O653" s="17">
+        <v>14</v>
+      </c>
+      <c r="P653" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q653" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R653" s="16" t="s">
+        <v>576</v>
+      </c>
+      <c r="S653" s="16" t="s">
+        <v>577</v>
+      </c>
+      <c r="T653" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="U653" s="18">
+        <v>46130</v>
+      </c>
+      <c r="V653" s="19">
+        <v>5</v>
+      </c>
+      <c r="W653" s="19">
+        <v>70</v>
+      </c>
+      <c r="X653" s="19">
+        <v>67900</v>
+      </c>
+      <c r="Y653" s="19">
+        <v>53014</v>
+      </c>
+      <c r="Z653" s="19">
+        <v>44758.89</v>
+      </c>
+      <c r="AA653" s="7"/>
+      <c r="AB653" s="19">
+        <v>-2904.84</v>
+      </c>
+      <c r="AC653" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD653" s="19">
+        <v>-70</v>
+      </c>
+      <c r="AE653" s="19">
+        <v>-835.68</v>
+      </c>
+      <c r="AF653" s="19">
+        <v>40948.370000000003</v>
+      </c>
+      <c r="AG653" s="19">
+        <v>48319.08</v>
+      </c>
+      <c r="AH653" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI653" s="19">
+        <v>7370.71</v>
+      </c>
+      <c r="AJ653" s="19">
+        <v>48319.08</v>
+      </c>
+      <c r="AK653" s="20">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="654" spans="1:37" s="24" customFormat="1" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A654" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B654" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C654" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D654" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E654" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="F654" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="G654" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="H654" s="15" t="s">
+        <v>575</v>
+      </c>
+      <c r="I654" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="J654" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="K654" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="L654" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="M654" s="15" t="s">
+        <v>558</v>
+      </c>
+      <c r="N654" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="O654" s="21">
+        <v>20</v>
+      </c>
+      <c r="P654" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q654" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="R654" s="15" t="s">
+        <v>576</v>
+      </c>
+      <c r="S654" s="15" t="s">
+        <v>577</v>
+      </c>
+      <c r="T654" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="U654" s="22">
+        <v>46130</v>
+      </c>
+      <c r="V654" s="21">
+        <v>20</v>
+      </c>
+      <c r="W654" s="21">
+        <v>400</v>
+      </c>
+      <c r="X654" s="21">
+        <v>124800</v>
+      </c>
+      <c r="Y654" s="21">
+        <v>93080</v>
+      </c>
+      <c r="Z654" s="21">
+        <v>80529.009999999995</v>
+      </c>
+      <c r="AA654" s="12"/>
+      <c r="AB654" s="21">
+        <v>-5701.44</v>
+      </c>
+      <c r="AC654" s="21">
+        <v>0</v>
+      </c>
+      <c r="AD654" s="21">
+        <v>-400</v>
+      </c>
+      <c r="AE654" s="21">
+        <v>-1488.55</v>
+      </c>
+      <c r="AF654" s="21">
+        <v>72939.02</v>
+      </c>
+      <c r="AG654" s="21">
+        <v>86068.04</v>
+      </c>
+      <c r="AH654" s="21">
+        <v>0</v>
+      </c>
+      <c r="AI654" s="21">
+        <v>13129.02</v>
+      </c>
+      <c r="AJ654" s="21">
+        <v>86068.04</v>
+      </c>
+      <c r="AK654" s="23">
+        <v>-0.04</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
